--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484718_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484718_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5337</v>
+        <v>8.533200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2041</v>
+        <v>9.886200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6704</v>
+        <v>-1.353</v>
       </c>
       <c r="G2" t="n">
         <v>4.4251</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3444</v>
+        <v>-0.3449</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9283</v>
+        <v>-0.2462</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4161</v>
+        <v>-0.0987</v>
       </c>
       <c r="V2" t="n">
         <v>2.1886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0518</v>
+        <v>2.1753</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6651</v>
+        <v>-1.3727</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7169</v>
+        <v>3.5479</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.8436</v>
+        <v>-1.0359</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1575</v>
+        <v>0.5486</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6862</v>
+        <v>-1.5845</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.9828</v>
+        <v>-0.9578</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3829</v>
+        <v>0.259</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5999</v>
+        <v>-1.2169</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1392</v>
+        <v>-0.078</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2254</v>
+        <v>0.2896</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0863</v>
+        <v>-0.3676</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1322</v>
+        <v>2.0757</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0757</v>
+        <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2162</v>
+        <v>-0.1098</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7141</v>
+        <v>-0.7165</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5021</v>
+        <v>0.6068</v>
       </c>
       <c r="V3" t="n">
-        <v>1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="W3" t="n">
-        <v>1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6624</v>
+        <v>1.7961</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8855</v>
+        <v>-1.4446</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5479</v>
+        <v>3.2407</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0359</v>
+        <v>-1.8436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5486</v>
+        <v>-1.1575</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5845</v>
+        <v>-0.6862</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9578</v>
+        <v>-1.9828</v>
       </c>
       <c r="K4" t="n">
-        <v>0.259</v>
+        <v>-1.3829</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2169</v>
+        <v>-0.5999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.078</v>
+        <v>0.1392</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2896</v>
+        <v>0.2254</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3676</v>
+        <v>-0.0863</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0192</v>
+        <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3774</v>
+        <v>0.9606</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2294</v>
+        <v>-0.0653</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6068</v>
+        <v>1.0259</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2452</v>
+        <v>1.547</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>1.547</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4582</v>
+        <v>0.9248</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7484</v>
+        <v>0.3747</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7098</v>
+        <v>0.5501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9756</v>
+        <v>0.6514</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7849</v>
+        <v>1.7835</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1906</v>
+        <v>-1.1321</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1599</v>
+        <v>1.5344</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0776</v>
+        <v>1.411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0823</v>
+        <v>0.1234</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1843</v>
+        <v>-0.8829</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2927</v>
+        <v>0.3725</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1083</v>
+        <v>-1.2555</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7548</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>-3.0192</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2374</v>
+        <v>-0.198</v>
       </c>
       <c r="T5" t="n">
-        <v>0.532</v>
+        <v>0.0107</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7055</v>
+        <v>-0.2087</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5796</v>
+        <v>0.9013</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0824</v>
+        <v>0.4561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4972</v>
+        <v>0.4453</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6514</v>
+        <v>0.9756</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7835</v>
+        <v>0.7849</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1321</v>
+        <v>0.1906</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5344</v>
+        <v>1.1599</v>
       </c>
       <c r="K6" t="n">
-        <v>1.411</v>
+        <v>1.0776</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1234</v>
+        <v>0.0823</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8829</v>
+        <v>-0.1843</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3725</v>
+        <v>-0.2927</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2555</v>
+        <v>0.1083</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6983</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0192</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5432</v>
+        <v>0.6806</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2816</v>
+        <v>0.2397</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2616</v>
+        <v>0.4409</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2286</v>
+        <v>-0.0086</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.564</v>
+        <v>-2.6614</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3354</v>
+        <v>2.6528</v>
       </c>
       <c r="G8" t="n">
         <v>0.7939000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>2.6418</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4938</v>
+        <v>-0.2738</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7026</v>
+        <v>-0.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2087</v>
+        <v>0.5262</v>
       </c>
       <c r="V8" t="n">
         <v>1.547</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3234</v>
+        <v>-1.2969</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1352</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1882</v>
+        <v>-1.1617</v>
       </c>
       <c r="G9" t="n">
         <v>-0.603</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2299</v>
+        <v>-0.2034</v>
       </c>
       <c r="T9" t="n">
         <v>0.0123</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2422</v>
+        <v>-0.2157</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3018</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4023</v>
+        <v>-1.4204</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6493</v>
+        <v>-1.7468</v>
       </c>
       <c r="F10" t="n">
-        <v>0.247</v>
+        <v>0.3264</v>
       </c>
       <c r="G10" t="n">
         <v>0.7044</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3839</v>
+        <v>0.3658</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0559</v>
+        <v>-0.1533</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4397</v>
+        <v>0.5191</v>
       </c>
       <c r="V10" t="n">
         <v>-1.547</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.554</v>
+        <v>-3.2881</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0729</v>
+        <v>-3.7806</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5189</v>
+        <v>0.4925</v>
       </c>
       <c r="G11" t="n">
         <v>-1.698</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8559</v>
+        <v>-0.59</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6343</v>
+        <v>-0.342</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2216</v>
+        <v>-0.248</v>
       </c>
       <c r="V11" t="n">
         <v>0.3208</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4449</v>
+        <v>-3.9842</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3017</v>
+        <v>-4.8145</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8568</v>
+        <v>0.8303</v>
       </c>
       <c r="G12" t="n">
         <v>-5.1451</v>
@@ -1390,13 +1390,13 @@
         <v>1.6983</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8094</v>
+        <v>-0.3487</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1046</v>
+        <v>-0.6175</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2952</v>
+        <v>0.2687</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.649499999999999</v>
+        <v>4.649500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.921800000000001</v>
+        <v>-4.9218</v>
       </c>
       <c r="F13" t="n">
-        <v>9.571300000000001</v>
+        <v>9.571299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.458200000000001</v>
+        <v>-2.4582</v>
       </c>
       <c r="H13" t="n">
         <v>10.3146</v>
@@ -1444,7 +1444,7 @@
         <v>2.966699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>9.030999999999999</v>
+        <v>9.031000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-6.0643</v>
@@ -1468,10 +1468,10 @@
         <v>16.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06169999999999987</v>
+        <v>-0.06159999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.6783</v>
+        <v>-2.6781</v>
       </c>
       <c r="U13" t="n">
         <v>2.616499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0598</v>
+        <v>4.2602</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4697</v>
+        <v>5.2492</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4099</v>
+        <v>-0.989</v>
       </c>
       <c r="G14" t="n">
         <v>5.9643</v>
@@ -1546,13 +1546,13 @@
         <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4332</v>
+        <v>-0.2328</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1758</v>
+        <v>-0.3963</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2574</v>
+        <v>0.1635</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7922</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9072</v>
+        <v>2.2078</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004</v>
+        <v>0.1989</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9031</v>
+        <v>2.009</v>
       </c>
       <c r="G15" t="n">
         <v>1.7022</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2481</v>
+        <v>0.0526</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.291</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.043</v>
+        <v>0.1488</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TAEÑO ELEZ</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2509</v>
+        <v>1.7104</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2509</v>
+        <v>0.6688</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.0416</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2509</v>
+        <v>1.7051</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6339</v>
+        <v>-1.0596</v>
       </c>
       <c r="I16" t="n">
-        <v>0.617</v>
+        <v>2.7648</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2509</v>
+        <v>0.8345</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6339</v>
+        <v>-0.5228</v>
       </c>
       <c r="L16" t="n">
-        <v>0.617</v>
+        <v>1.3573</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.8706</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.5369</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.4075</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.2591</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.1657</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.0934</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>M. TAEÑO ELEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2088</v>
+        <v>1.2509</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3765</v>
+        <v>1.2509</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8323</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7051</v>
+        <v>1.2509</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0596</v>
+        <v>0.6339</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7648</v>
+        <v>0.617</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8345</v>
+        <v>1.2509</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5228</v>
+        <v>0.6339</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3573</v>
+        <v>0.617</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8706</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5369</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4075</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7607</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.458</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3027</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0133</v>
+        <v>0.6238</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.2867</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6801</v>
+        <v>0.9106</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3134</v>
+        <v>-1.0885</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.1902</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4896</v>
+        <v>-0.8983</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0358</v>
+        <v>-0.0315</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2004</v>
+        <v>1.062</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1645</v>
+        <v>-1.0935</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2775</v>
+        <v>-1.057</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6026</v>
+        <v>-1.2521</v>
       </c>
       <c r="O18" t="n">
-        <v>0.325</v>
+        <v>0.1951</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8553</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6525</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2028</v>
+        <v>0.458</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6036</v>
+        <v>0.3018</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6036</v>
+        <v>0.3018</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2991</v>
+        <v>-0.1713</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4816</v>
+        <v>-1.3488</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7806</v>
+        <v>1.1775</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0885</v>
+        <v>-0.3134</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1902</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8983</v>
+        <v>0.4896</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0315</v>
+        <v>-0.0358</v>
       </c>
       <c r="K19" t="n">
-        <v>1.062</v>
+        <v>-0.2004</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0935</v>
+        <v>0.1645</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.057</v>
+        <v>-0.2775</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2521</v>
+        <v>-0.6026</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1951</v>
+        <v>0.325</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5096</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4238</v>
+        <v>0.6706</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7519</v>
+        <v>-0.0296</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3281</v>
+        <v>0.7002</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3018</v>
+        <v>0.6036</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3018</v>
+        <v>0.6036</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.251</v>
+        <v>-0.5386</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2653</v>
+        <v>-1.9474</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0143</v>
+        <v>1.4088</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3127</v>
@@ -2014,13 +2014,13 @@
         <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6278</v>
+        <v>0.3402</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.0292</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0835</v>
+        <v>0.311</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4098</v>
+        <v>-1.4255</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2824</v>
+        <v>-1.2464</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8727</v>
+        <v>-0.179</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2919</v>
+        <v>0.108</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3774</v>
+        <v>0.5564</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6693</v>
+        <v>-0.4484</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6077</v>
+        <v>0.4125</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1738</v>
+        <v>1.0776</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7815</v>
+        <v>-0.6651</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3158</v>
+        <v>-0.3045</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2036</v>
+        <v>-0.5212</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8878</v>
+        <v>0.2167</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1286</v>
+        <v>-0.0054</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9028</v>
+        <v>-0.3946</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2258</v>
+        <v>0.3892</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5094</v>
+        <v>-1.528</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.019</v>
+        <v>-0.3208</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4904</v>
+        <v>-1.2072</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2036</v>
+        <v>-2.871</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7336</v>
+        <v>-3.1593</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.47</v>
+        <v>0.2883</v>
       </c>
       <c r="G22" t="n">
-        <v>0.108</v>
+        <v>0.2919</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5564</v>
+        <v>-1.3774</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4484</v>
+        <v>1.6693</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4125</v>
+        <v>0.6077</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0776</v>
+        <v>-0.1738</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6651</v>
+        <v>0.7815</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3045</v>
+        <v>-0.3158</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5212</v>
+        <v>-1.2036</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2167</v>
+        <v>0.8878</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7836</v>
+        <v>0.6673</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8818</v>
+        <v>0.0259</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0982</v>
+        <v>0.6414</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.528</v>
+        <v>-2.5094</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3208</v>
+        <v>-0.019</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2072</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3605</v>
+        <v>-4.025</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4127</v>
+        <v>-5.3153</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0522</v>
+        <v>1.2903</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4027</v>
@@ -2248,13 +2248,13 @@
         <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6178</v>
+        <v>-0.2823</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4551</v>
+        <v>-0.3576</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1628</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>1.547</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1636</v>
+        <v>-5.0216</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8301</v>
+        <v>-3.6352</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3335</v>
+        <v>-1.3864</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4469</v>
@@ -2326,13 +2326,13 @@
         <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2828</v>
+        <v>-0.1408</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.6746</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5867</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.649399999999999</v>
+        <v>-3.999900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.571400000000001</v>
+        <v>-9.571300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>4.9219</v>
+        <v>5.5717</v>
       </c>
       <c r="G25" t="n">
-        <v>2.458200000000001</v>
+        <v>2.458199999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-10.3147</v>
@@ -2383,7 +2383,7 @@
         <v>-1.2838</v>
       </c>
       <c r="L25" t="n">
-        <v>6.708600000000001</v>
+        <v>6.708599999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-2.9666</v>
@@ -2404,13 +2404,13 @@
         <v>16.0395</v>
       </c>
       <c r="S25" t="n">
-        <v>0.06169999999999981</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6166</v>
+        <v>-2.6165</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6782</v>
+        <v>3.3278</v>
       </c>
       <c r="V25" t="n">
         <v>-7.1694</v>
